--- a/test/fixtures/r1-chart.xlsx
+++ b/test/fixtures/r1-chart.xlsx
@@ -238,30 +238,30 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5400000" cy="2700000"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm/>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
